--- a/AAII_Financials/Quarterly/RPRX_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RPRX_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="92">
   <si>
     <t>RPRX</t>
   </si>
@@ -656,290 +656,297 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="34" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="35" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AG7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AH7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>674100</v>
+      </c>
+      <c r="E8" s="3">
         <v>630600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>622000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>609300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>578700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>568200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>593600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>564700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>537300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>568000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>596100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>536300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>538200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>684000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>565700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>573500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>536000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>562000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>575700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>585800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>555000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>573000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>572100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>538400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>510900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>500900</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>457500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>457600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>434900</v>
       </c>
-      <c r="AF8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>268200</v>
+      </c>
+      <c r="E9" s="3">
         <v>-197500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>23100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>12100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>-203900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>-127100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>164000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>-227600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>212400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>583600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>-76500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>277100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>241200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>118800</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
@@ -991,53 +998,56 @@
       <c r="AH9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>405900</v>
+      </c>
+      <c r="E10" s="3">
         <v>828100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>598900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>597200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>782600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>695400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>429600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>792300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>324800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-15600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>672600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>259200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>297000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>565200</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1089,8 +1099,11 @@
       <c r="AH10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1125,28 +1138,29 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>97900</v>
+      </c>
+      <c r="E12" s="3">
         <v>39800</v>
-      </c>
-      <c r="E12" s="3">
-        <v>50500</v>
       </c>
       <c r="F12" s="3">
         <v>50500</v>
       </c>
       <c r="G12" s="3">
+        <v>50500</v>
+      </c>
+      <c r="H12" s="3">
         <v>300500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>50500</v>
-      </c>
-      <c r="I12" s="3">
-        <v>500</v>
       </c>
       <c r="J12" s="3">
         <v>500</v>
@@ -1161,70 +1175,73 @@
         <v>500</v>
       </c>
       <c r="N12" s="3">
+        <v>500</v>
+      </c>
+      <c r="O12" s="3">
         <v>50500</v>
-      </c>
-      <c r="O12" s="3">
-        <v>500</v>
       </c>
       <c r="P12" s="3">
         <v>500</v>
       </c>
       <c r="Q12" s="3">
+        <v>500</v>
+      </c>
+      <c r="R12" s="3">
         <v>50500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>25500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>100500</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>103800</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>90500</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>3100</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>2600</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>7800</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>5100</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>5800</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>7600</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>15900</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>21500</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>23000</v>
       </c>
-      <c r="AF12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG12" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,56 +1338,59 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-34300</v>
+      </c>
+      <c r="E14" s="3">
         <v>96300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-89400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-70300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>73000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>49200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-9100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-108500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>47300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-124200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-163500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-8800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-124200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-21500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>615800</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1389,15 +1409,15 @@
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z14" s="3">
         <v>5400</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>25100</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1410,8 +1430,8 @@
       <c r="AE14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
+      <c r="AF14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AG14" s="3">
         <v>0</v>
@@ -1419,26 +1439,29 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="E15" s="3">
         <v>1200</v>
       </c>
       <c r="F15" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G15" s="3">
         <v>1300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>700</v>
       </c>
-      <c r="H15" s="3">
-        <v>0</v>
-      </c>
       <c r="I15" s="3">
         <v>0</v>
       </c>
@@ -1452,7 +1475,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="3">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="N15" s="3">
         <v>1400</v>
@@ -1464,7 +1487,7 @@
         <v>1400</v>
       </c>
       <c r="Q15" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="R15" s="3">
         <v>0</v>
@@ -1473,52 +1496,55 @@
         <v>0</v>
       </c>
       <c r="T15" s="3">
+        <v>0</v>
+      </c>
+      <c r="U15" s="3">
         <v>5700</v>
-      </c>
-      <c r="U15" s="3">
-        <v>5800</v>
       </c>
       <c r="V15" s="3">
         <v>5800</v>
       </c>
       <c r="W15" s="3">
-        <v>5700</v>
+        <v>5800</v>
       </c>
       <c r="X15" s="3">
         <v>5700</v>
       </c>
       <c r="Y15" s="3">
-        <v>5800</v>
+        <v>5700</v>
       </c>
       <c r="Z15" s="3">
         <v>5800</v>
       </c>
       <c r="AA15" s="3">
-        <v>5700</v>
+        <v>5800</v>
       </c>
       <c r="AB15" s="3">
         <v>5700</v>
       </c>
       <c r="AC15" s="3">
+        <v>5700</v>
+      </c>
+      <c r="AD15" s="3">
         <v>5800</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>5700</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>6600</v>
       </c>
-      <c r="AF15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG15" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH15" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>541000</v>
+      </c>
+      <c r="E17" s="3">
         <v>-1900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>263200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>181100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>353900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>34100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>232100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>-170400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>267600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>641800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>-16800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>384900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>289400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>205000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1048400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>381300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>158200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>342300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>422300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>282700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>-190000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>343700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>263500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>52900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>101600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>139400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>-874400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>129700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>4000</v>
       </c>
-      <c r="AF17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>133100</v>
+      </c>
+      <c r="E18" s="3">
         <v>632500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>358800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>428200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>224800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>534200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>361500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>735100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>269600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-73800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>612900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>151400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>248800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>479000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-482700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>192200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>377800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>219700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>153400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>303100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>745000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>229300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>308600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>485500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>409300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>361500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>1331900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>327900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>430900</v>
       </c>
-      <c r="AF18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,245 +1815,252 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-2600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-19600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>5200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-18400</v>
       </c>
-      <c r="G20" s="3">
-        <v>900</v>
-      </c>
       <c r="H20" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="I20" s="3">
         <v>-3400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-20500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-11800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-7700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>17800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>18000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>15600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-38900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-80400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>75100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>160700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-44500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-52800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-37000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>99200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-32900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>95900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>170200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>226900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-198800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>177900</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-79900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>32400</v>
       </c>
-      <c r="AF20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG20" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>137000</v>
+      </c>
+      <c r="E21" s="3">
         <v>653200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>354800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>447800</v>
       </c>
-      <c r="G21" s="3">
-        <v>224600</v>
-      </c>
       <c r="H21" s="3">
+        <v>226600</v>
+      </c>
+      <c r="I21" s="3">
         <v>537600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>382000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>746800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>277300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-91600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>596300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>137300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>249900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>519300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-563100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>267400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>538600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>180800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>106400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>271900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>849900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>202100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>410300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>661500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>641900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>168400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1515700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>253700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>470000</v>
       </c>
-      <c r="AF21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>93600</v>
+      </c>
+      <c r="E22" s="3">
         <v>93700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>94200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>79600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>68700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>65300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>65800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>66500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>49000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>44200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>47300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>46000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>46900</v>
-      </c>
-      <c r="P22" s="3">
-        <v>47000</v>
       </c>
       <c r="Q22" s="3">
         <v>47000</v>
@@ -2032,150 +2072,156 @@
         <v>47000</v>
       </c>
       <c r="T22" s="3">
+        <v>47000</v>
+      </c>
+      <c r="U22" s="3">
         <v>47100</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>47000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>44300</v>
-      </c>
-      <c r="W22" s="3">
-        <v>37400</v>
       </c>
       <c r="X22" s="3">
         <v>37400</v>
       </c>
       <c r="Y22" s="3">
+        <v>37400</v>
+      </c>
+      <c r="Z22" s="3">
         <v>37800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>31400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>34200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>53600</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>63300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>69200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>67300</v>
       </c>
-      <c r="AF22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH22" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>81500</v>
+      </c>
+      <c r="E23" s="3">
         <v>468300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>355900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>444200</v>
       </c>
-      <c r="G23" s="3">
-        <v>90600</v>
-      </c>
       <c r="H23" s="3">
+        <v>92600</v>
+      </c>
+      <c r="I23" s="3">
         <v>434400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>334400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>806400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>194400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-4300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>717600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>122100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>351300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>509100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-610000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>220400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>491600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>128100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>53700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>221800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>806800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>159000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>366600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>624300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>602000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>109100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>1446500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>178800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>396100</v>
       </c>
-      <c r="AF23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2218,8 +2264,8 @@
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R24" s="3">
         <v>0</v>
@@ -2272,8 +2318,11 @@
       <c r="AH24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>81500</v>
+      </c>
+      <c r="E26" s="3">
         <v>468300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>355900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>444200</v>
       </c>
-      <c r="G26" s="3">
-        <v>90600</v>
-      </c>
       <c r="H26" s="3">
+        <v>92600</v>
+      </c>
+      <c r="I26" s="3">
         <v>434400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>334400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>806400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>194400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-4300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>717600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>122100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>351300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>509100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-610000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>220400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>491600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>128100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>53700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>221800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>806800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>159000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>366600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>624300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>602000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>109100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>1446500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>178800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>396100</v>
       </c>
-      <c r="AF26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>17900</v>
+      </c>
+      <c r="E27" s="3">
         <v>294700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>214200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>288200</v>
       </c>
-      <c r="G27" s="3">
-        <v>30200</v>
-      </c>
       <c r="H27" s="3">
+        <v>32200</v>
+      </c>
+      <c r="I27" s="3">
         <v>239300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>208200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>544000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>102000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>494300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>72100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>227600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>340800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-456100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>142700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>304500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>51800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>7900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>101900</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>440800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>69100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>171100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>290600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>33500</v>
       </c>
-      <c r="AB27" s="3">
-        <v>0</v>
-      </c>
       <c r="AC27" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD27" s="3">
         <v>1420400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>151700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>367400</v>
       </c>
-      <c r="AF27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,204 +3025,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E32" s="3">
         <v>19600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-5200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>18400</v>
       </c>
-      <c r="G32" s="3">
-        <v>-900</v>
-      </c>
       <c r="H32" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I32" s="3">
         <v>3400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>20500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>11800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>7700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-17800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-18000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-15600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>38900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>80400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-75100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-160700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>44500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>52800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>37000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-99200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>32900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-95900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-170200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-226900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>198800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-177900</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>79900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-32400</v>
       </c>
-      <c r="AF32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG32" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>17900</v>
+      </c>
+      <c r="E33" s="3">
         <v>294700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>214200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>288200</v>
       </c>
-      <c r="G33" s="3">
-        <v>30200</v>
-      </c>
       <c r="H33" s="3">
+        <v>32200</v>
+      </c>
+      <c r="I33" s="3">
         <v>239300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>208200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>544000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>102000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>494300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>72100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>227600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>340800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-456100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>142700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>304500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>51800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>7900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>101900</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>440800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>69100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>171100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>290600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>33500</v>
       </c>
-      <c r="AB33" s="3">
-        <v>0</v>
-      </c>
       <c r="AC33" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD33" s="3">
         <v>1420400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>151700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>367400</v>
       </c>
-      <c r="AF33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>17900</v>
+      </c>
+      <c r="E35" s="3">
         <v>294700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>214200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>288200</v>
       </c>
-      <c r="G35" s="3">
-        <v>30200</v>
-      </c>
       <c r="H35" s="3">
+        <v>32200</v>
+      </c>
+      <c r="I35" s="3">
         <v>239300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>208200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>544000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>102000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>494300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>72100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>227600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>340800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-456100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>142700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>304500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>51800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>7900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>101900</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>440800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>69100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>171100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>290600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>33500</v>
       </c>
-      <c r="AB35" s="3">
-        <v>0</v>
-      </c>
       <c r="AC35" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD35" s="3">
         <v>1420400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>151700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>367400</v>
       </c>
-      <c r="AF35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AG38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AH38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,89 +3611,90 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>812000</v>
+      </c>
+      <c r="E41" s="3">
         <v>586400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>618700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>938900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>631900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1087700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>929000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>950100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1764600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>843000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>477000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>936400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2173100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1975700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1710800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>991600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2108000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1791500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1541000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1800800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1142300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>708800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1008700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1552800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2443400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>624400</v>
       </c>
-      <c r="AC41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD41" s="3" t="s">
         <v>3</v>
       </c>
@@ -3623,89 +3710,92 @@
       <c r="AH41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E42" s="3">
         <v>21900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>18800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>16100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>13200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>12100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>58200</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>48500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>38500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>29000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>18300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>5300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>5100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>2500</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>717000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>1225100</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>1293300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>1119700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>1262200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>892500</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>1508200</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>1660600</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>1640500</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>1179900</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>899100</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>1071800</v>
       </c>
-      <c r="AC42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD42" s="3" t="s">
         <v>3</v>
       </c>
@@ -3721,89 +3811,92 @@
       <c r="AH42" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>920900</v>
+      </c>
+      <c r="E43" s="3">
         <v>807400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>883700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>889000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>870700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>740300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>810700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>790700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>773700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>682700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>760800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>780100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>765100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>648500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>36600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>34800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>35300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>65800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>68300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>73500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>44800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>40000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>39200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>36800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>35500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>41600</v>
       </c>
-      <c r="AC43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD43" s="3" t="s">
         <v>3</v>
       </c>
@@ -3819,8 +3912,11 @@
       <c r="AH43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3863,8 +3959,8 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -3917,89 +4013,92 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>6700</v>
+      </c>
+      <c r="E45" s="3">
         <v>10200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>6900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>5500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>4200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>5000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>2300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>5000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>18000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>6800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>10200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4600</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>90500</v>
       </c>
       <c r="R45" s="3">
         <v>90500</v>
       </c>
       <c r="S45" s="3">
+        <v>90500</v>
+      </c>
+      <c r="T45" s="3">
         <v>67100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>5400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>6600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>8900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>12100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>6700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>8600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>14400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>12800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>100</v>
       </c>
-      <c r="AC45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD45" s="3" t="s">
         <v>3</v>
       </c>
@@ -4015,89 +4114,92 @@
       <c r="AH45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1764600</v>
+      </c>
+      <c r="E46" s="3">
         <v>1425800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1528100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1849500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1520200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1843200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1802100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1794200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2579100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1559700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1274200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1728600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2953500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2631200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2554900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>2342100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3503800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>2982400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>2878200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>2775800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>2707500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>2416000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2696900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2783900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3390800</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1737800</v>
       </c>
-      <c r="AC46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD46" s="3" t="s">
         <v>3</v>
       </c>
@@ -4113,89 +4215,92 @@
       <c r="AH46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>876000</v>
+      </c>
+      <c r="E47" s="3">
         <v>845800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>880300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>722900</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>658300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>696300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1259900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1237200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1160000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1101300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1012500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>876200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>870800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>753100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>14228900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>15299900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>14203200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>14392600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>14627800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>14940600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>13784200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>13467900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>13266100</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>13159800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>12239800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>11573100</v>
       </c>
-      <c r="AC47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD47" s="3" t="s">
         <v>3</v>
       </c>
@@ -4211,26 +4316,29 @@
       <c r="AH47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E48" s="3">
         <v>18300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>19100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>19800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>20600</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4255,8 +4363,8 @@
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q48" s="3">
-        <v>0</v>
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R48" s="3">
         <v>0</v>
@@ -4309,25 +4417,28 @@
       <c r="AH48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>924600</v>
+        <v>923500</v>
       </c>
       <c r="E49" s="3">
         <v>924600</v>
       </c>
       <c r="F49" s="3">
-        <v>930000</v>
+        <v>924600</v>
       </c>
       <c r="G49" s="3">
         <v>930000</v>
       </c>
       <c r="H49" s="3">
-        <v>5300</v>
+        <v>930000</v>
       </c>
       <c r="I49" s="3">
         <v>5300</v>
@@ -4339,23 +4450,23 @@
         <v>5300</v>
       </c>
       <c r="L49" s="3">
-        <v>0</v>
+        <v>5300</v>
       </c>
       <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3">
         <v>1800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>16300</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>16600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>14200</v>
       </c>
-      <c r="Q49" s="3">
-        <v>0</v>
-      </c>
       <c r="R49" s="3">
         <v>0</v>
       </c>
@@ -4366,32 +4477,32 @@
         <v>0</v>
       </c>
       <c r="U49" s="3">
+        <v>0</v>
+      </c>
+      <c r="V49" s="3">
         <v>5700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>11500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>17300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>23000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>28700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>34500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>40300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>46000</v>
       </c>
-      <c r="AC49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD49" s="3" t="s">
         <v>3</v>
       </c>
@@ -4407,8 +4518,11 @@
       <c r="AH49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,88 +4720,91 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>63000</v>
+      </c>
+      <c r="E52" s="3">
         <v>58600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>60200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>61500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>59600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>31400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>28200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>37500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>22200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>12800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>13800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>29600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>30600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>33400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>4100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>4500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>6000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>7100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>28600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>12500</v>
-      </c>
-      <c r="AA52" s="3">
-        <v>14700</v>
       </c>
       <c r="AB52" s="3">
         <v>14700</v>
       </c>
-      <c r="AC52" s="3" t="s">
-        <v>3</v>
+      <c r="AC52" s="3">
+        <v>14700</v>
       </c>
       <c r="AD52" s="3" t="s">
         <v>3</v>
@@ -4701,8 +4821,11 @@
       <c r="AH52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,89 +4922,92 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>19819800</v>
+      </c>
+      <c r="E54" s="3">
         <v>19815400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>19620800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>19347300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>18323000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>17608300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>18222700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>18042200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>17656600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>16130900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>16381900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>15855500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>17121500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>17074100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>16813500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>17672600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>17740400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>17378900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>17515900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>17732400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>16514900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>15914100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>16020300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>15990700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>15685600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>13371600</v>
       </c>
-      <c r="AC54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4897,8 +5023,11 @@
       <c r="AH54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,89 +5099,90 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>35600</v>
+      </c>
+      <c r="E57" s="3">
         <v>25500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>19400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>41400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>20200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>37600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>13400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>22100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>23400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>11600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>15200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>13600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>6700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>7900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>16100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>12200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>6700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>5600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>9200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>9400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>8300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>10800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>24400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>34400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>20800</v>
       </c>
-      <c r="AC57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD57" s="3" t="s">
         <v>3</v>
       </c>
@@ -5067,35 +5198,38 @@
       <c r="AH57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>383200</v>
+        <v>380000</v>
       </c>
       <c r="E58" s="3">
         <v>383200</v>
       </c>
       <c r="F58" s="3">
+        <v>383200</v>
+      </c>
+      <c r="G58" s="3">
         <v>383100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1002500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>998600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>997800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>996900</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -5106,20 +5240,20 @@
         <v>0</v>
       </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>999400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>998400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>997500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>996600</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
@@ -5135,21 +5269,21 @@
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y58" s="3">
-        <v>0</v>
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z58" s="3">
         <v>0</v>
       </c>
       <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="3">
         <v>182200</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>182100</v>
       </c>
-      <c r="AC58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD58" s="3" t="s">
         <v>3</v>
       </c>
@@ -5165,89 +5299,92 @@
       <c r="AH58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>107600</v>
+      </c>
+      <c r="E59" s="3">
         <v>101700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>122800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>77200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>98200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>127400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>144400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>110300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>196000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>100400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>94500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>101700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>112900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>98600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>161400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>118900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>170200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>129200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>165600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>245900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>274600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>247700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>297100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>245600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>234400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>231100</v>
       </c>
-      <c r="AC59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD59" s="3" t="s">
         <v>3</v>
       </c>
@@ -5263,89 +5400,92 @@
       <c r="AH59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>630900</v>
+      </c>
+      <c r="E60" s="3">
         <v>535700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>636200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>530800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1206500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1182900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1253600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1167800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>275700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>124600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>161400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>127900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1172200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1116900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1166800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1131600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>182300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>135900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>171300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>255100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>284000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>256000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>307900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>270000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>451000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>434000</v>
       </c>
-      <c r="AC60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD60" s="3" t="s">
         <v>3</v>
       </c>
@@ -5361,89 +5501,92 @@
       <c r="AH60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>8581900</v>
+      </c>
+      <c r="E61" s="3">
         <v>8591700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>8587000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>8582600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>7020800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6618800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6614700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>6610400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>7602000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>6139400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>6135300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6131200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>6127100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>6122900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>6118800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>6114700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>7106200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>7101100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>7096100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>7090700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>5825600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>5821100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>5816600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>5812000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>5729600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>5775000</v>
       </c>
-      <c r="AC61" s="3">
-        <v>0</v>
-      </c>
       <c r="AD61" s="3">
         <v>0</v>
       </c>
@@ -5459,62 +5602,65 @@
       <c r="AH61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>821200</v>
+      </c>
+      <c r="E62" s="3">
         <v>751200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>682600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>613000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>592800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>17900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>12100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>5600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>27000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>11300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>8500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>12300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>2500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>9900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>43700</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5527,20 +5673,20 @@
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y62" s="3">
-        <v>0</v>
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z62" s="3">
-        <v>110000</v>
+        <v>0</v>
       </c>
       <c r="AA62" s="3">
         <v>110000</v>
       </c>
       <c r="AB62" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC62" s="3" t="s">
-        <v>3</v>
+        <v>110000</v>
+      </c>
+      <c r="AC62" s="3">
+        <v>0</v>
       </c>
       <c r="AD62" s="3" t="s">
         <v>3</v>
@@ -5557,8 +5703,11 @@
       <c r="AH62" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI62" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,89 +6006,92 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>10034100</v>
+      </c>
+      <c r="E66" s="3">
         <v>9878600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>9905800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>9726400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>8820100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7819600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>7880300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7783800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7904800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6267200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6297600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>6270400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>7307800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>7252100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>11185300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>11520500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>11713200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>11601300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>11739300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>11939300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>10781200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>11031900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>11201500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>11538900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>11528400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>8211700</v>
       </c>
-      <c r="AC66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD66" s="3" t="s">
         <v>3</v>
       </c>
@@ -5949,8 +6107,11 @@
       <c r="AH66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,89 +6548,92 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2459100</v>
+      </c>
+      <c r="E72" s="3">
         <v>2507100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2356300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2304300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2222800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2480700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2845700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2764700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2378300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2427400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2517600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2134700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2252900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2216800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1964700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2505000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2446100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2224700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2255200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2320900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2292000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1923800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1920600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1807100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1571400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2562000</v>
       </c>
-      <c r="AC72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD72" s="3" t="s">
         <v>3</v>
       </c>
@@ -6475,8 +6649,11 @@
       <c r="AH72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,89 +6952,92 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6832700</v>
+      </c>
+      <c r="E76" s="3">
         <v>6888500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6476900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>6414300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>6347900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>6688600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>6946600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6869900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>6476300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6499800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6526500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>6138900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>6281700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>5953700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>5628200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>6152100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>6027200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>5777600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>5776600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>5793100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>5733700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4882200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4818800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4451800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4157100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>5159900</v>
       </c>
-      <c r="AC76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AD76" s="3" t="s">
         <v>3</v>
       </c>
@@ -6867,8 +7053,11 @@
       <c r="AH76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AG80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AH80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>17900</v>
+      </c>
+      <c r="E81" s="3">
         <v>294700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>214200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>288200</v>
       </c>
-      <c r="G81" s="3">
-        <v>30200</v>
-      </c>
       <c r="H81" s="3">
+        <v>32200</v>
+      </c>
+      <c r="I81" s="3">
         <v>239300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>208200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>544000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>102000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>494300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>72100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>227600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>340800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-456100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>142700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>304500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>51800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>7900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>101900</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>440800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>69100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>171100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>290600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>33500</v>
       </c>
-      <c r="AB81" s="3">
-        <v>0</v>
-      </c>
       <c r="AC81" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD81" s="3">
         <v>1420400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>151700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>367400</v>
       </c>
-      <c r="AF81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,13 +7400,14 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>3</v>
+      <c r="D83" s="3">
+        <v>1400</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>3</v>
@@ -7246,8 +7445,8 @@
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R83" s="3">
         <v>0</v>
@@ -7256,52 +7455,55 @@
         <v>0</v>
       </c>
       <c r="T83" s="3">
+        <v>0</v>
+      </c>
+      <c r="U83" s="3">
         <v>5700</v>
-      </c>
-      <c r="U83" s="3">
-        <v>5800</v>
       </c>
       <c r="V83" s="3">
         <v>5800</v>
       </c>
       <c r="W83" s="3">
-        <v>5700</v>
+        <v>5800</v>
       </c>
       <c r="X83" s="3">
         <v>5700</v>
       </c>
       <c r="Y83" s="3">
-        <v>5800</v>
+        <v>5700</v>
       </c>
       <c r="Z83" s="3">
         <v>5800</v>
       </c>
       <c r="AA83" s="3">
-        <v>5700</v>
+        <v>5800</v>
       </c>
       <c r="AB83" s="3">
         <v>5700</v>
       </c>
       <c r="AC83" s="3">
+        <v>5700</v>
+      </c>
+      <c r="AD83" s="3">
         <v>5800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>5700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>6600</v>
       </c>
-      <c r="AF83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG83" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>728500</v>
+      </c>
+      <c r="E89" s="3">
         <v>718200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>827100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>702600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>364000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>596100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>742500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>703600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>658200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>664600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>772600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>573500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>607800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1033800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>569900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>538800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>575000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>460300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>490000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>469800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>531700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>526100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>565700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>508800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>489000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>471100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>478400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>336900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>432900</v>
       </c>
-      <c r="AF89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG89" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,8 +8144,9 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -7968,62 +8189,65 @@
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R91" s="3">
         <v>-250200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1316300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-175000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-171700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-1336000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-180700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-503100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-805200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-802500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-475300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-99300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-466800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-23500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-1208300</v>
       </c>
-      <c r="AF91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG91" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,106 +8445,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-229700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-477900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-847800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-958300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-312000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>503900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-505600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1192700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-893200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-86700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1000200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-450700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-63400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-558500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>414700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1425200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-30200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>11200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-551600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-845500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>126200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-599300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-832400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1004600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-249400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-672900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-25300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-158400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-1317200</v>
       </c>
-      <c r="AF94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG94" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,80 +8585,81 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>104900</v>
+      </c>
+      <c r="E96" s="3">
         <v>104500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>94300</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>95300</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>93200</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>95400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>93700</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>94100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>94900</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>93800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>89300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>89800</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>90600</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>88600</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-84200</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-83800</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-83000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-82300</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-73600</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-73000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-72600</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-66000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-57600</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
         <v>0</v>
       </c>
@@ -8450,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,106 +8987,112 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-273100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-272700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-299600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>562700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-507800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-941300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-258000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-325500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1156600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-212000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-231900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1359500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-347000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-210400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-265600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-230100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-228300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-221000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-198100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1034300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-224400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-226700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-277400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-357400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>1579400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>542500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-285800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-310200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-315000</v>
       </c>
-      <c r="AF100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG100" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8886,8 +9135,8 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -8940,102 +9189,108 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>225600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-32300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-320200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>307000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-455800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>158700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-21000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-814600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>921600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>366000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-459400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1236600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>197400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>264900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>719100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1116400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>316500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>250500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-259800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>658500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>433500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-299900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-544100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-853100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1819100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>340700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>167300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-131700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1199200</v>
       </c>
-      <c r="AF102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AG102" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AH102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
